--- a/artfynd/A 64030-2023 artfynd.xlsx
+++ b/artfynd/A 64030-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64030-2023 artfynd.xlsx
+++ b/artfynd/A 64030-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,135 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118066126</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57287</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bräntkullarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>574255</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7172589</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två granar</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64030-2023 artfynd.xlsx
+++ b/artfynd/A 64030-2023 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>118066126</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 64030-2023 artfynd.xlsx
+++ b/artfynd/A 64030-2023 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>118066126</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 64030-2023 artfynd.xlsx
+++ b/artfynd/A 64030-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>97708779</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574190.8450939631</v>
+        <v>574191</v>
       </c>
       <c r="R2" t="n">
-        <v>7172680.565078793</v>
+        <v>7172681</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2021-12-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-12-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,65 +773,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118066126</v>
+        <v>97708826</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräntkullarna, Ås lm</t>
+          <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574255</v>
+        <v>574242</v>
       </c>
       <c r="R3" t="n">
-        <v>7172589</v>
+        <v>7172708</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,27 +839,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2021-12-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två granar</t>
+          <t>2021-12-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,15 +859,243 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Anna-Sara Karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anna-Sara Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118066126</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bräntkullarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>574255</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7172589</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två granar</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Jörgen Olsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Jörgen Olsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>97707626</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vilhelmina, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>574304</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7172593</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-12-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-12-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna-Sara Karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna-Sara Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
